--- a/artfynd/A 58422-2025 artfynd.xlsx
+++ b/artfynd/A 58422-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2000828</v>
+        <v>258865</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510354.8781836106</v>
+        <v>510361</v>
       </c>
       <c r="R2" t="n">
-        <v>6956490.748200712</v>
+        <v>6956295</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2012-11-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2012-11-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,16 +775,11 @@
         <v>1330871</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510331.6922650516</v>
+        <v>510332</v>
       </c>
       <c r="R3" t="n">
-        <v>6956418.241591214</v>
+        <v>6956418</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,19 +840,9 @@
           <t>2012-11-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-11-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>258865</v>
+        <v>1330873</v>
       </c>
       <c r="B4" t="n">
-        <v>89952</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>760</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510360.5437463211</v>
+        <v>510356</v>
       </c>
       <c r="R4" t="n">
-        <v>6956295.007708848</v>
+        <v>6956263</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -972,19 +937,9 @@
           <t>2012-11-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2012-11-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,16 +969,11 @@
         <v>80557793</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510384.0887987282</v>
+        <v>510384</v>
       </c>
       <c r="R5" t="n">
-        <v>6956544.935256275</v>
+        <v>6956545</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1120,6 +1070,103 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2000828</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sidsjö, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>510355</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6956491</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bodsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2012-11-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2012-11-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>SCA Naturvärdesinventeringar</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Acker</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
